--- a/data/trans_orig/IP1005-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249956</t>
+          <t>249355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248496</t>
+          <t>248448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253154</t>
+          <t>253156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>500378</t>
+          <t>500958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506285</t>
+          <t>506314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123053</t>
+          <t>123338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265029</t>
+          <t>264478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>675833</t>
+          <t>676357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717355</t>
+          <t>716681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722099</t>
+          <t>722098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1395427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401905</t>
+          <t>1402375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230136</t>
+          <t>230380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263743</t>
+          <t>263477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>496637</t>
+          <t>496070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151504</t>
+          <t>151119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155148</t>
+          <t>154688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308659</t>
+          <t>309332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701655</t>
+          <t>702025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>706486</t>
+          <t>706491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>744066</t>
+          <t>743397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448271</t>
+          <t>1447737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453945</t>
+          <t>1453967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127712</t>
+          <t>127748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251929</t>
+          <t>252034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206716</t>
+          <t>205981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251904</t>
+          <t>251687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257388</t>
+          <t>257386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>461073</t>
+          <t>460849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>467343</t>
+          <t>467282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>186834</t>
+          <t>186504</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>185734</t>
+          <t>185357</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373428</t>
+          <t>373498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170437</t>
+          <t>169770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343755</t>
+          <t>343422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>698404</t>
+          <t>698706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>703887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736743</t>
+          <t>736654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>743375</t>
+          <t>743461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1438180</t>
+          <t>1437660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1445937</t>
+          <t>1446014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1005-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5279</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5308</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>251775</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>248477</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253153</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>252563</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>249355</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>250205</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>251775</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>248448</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253156</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>757</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>500958</t>
+          <t>500405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506314</t>
+          <t>506263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4210</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4477</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4629</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4585</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>126242</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>123338</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123071</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>401</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264478</t>
+          <t>264434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2099,67 +2099,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5742</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6019</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720719</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>716907</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722098</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679073</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676357</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680388</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>675279</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680389</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720719</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>716681</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722098</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395427</t>
+          <t>1395102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402375</t>
+          <t>1402348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3383</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1137</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4096</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3621</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3624</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>266429</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>263718</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>233339</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>230380</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>230855</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>266429</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>263477</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>705</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>496070</t>
+          <t>496560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>501135</t>
+          <t>501133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,102 +3360,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3372</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3703</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3883</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4680</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4073</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3468,102 +3468,102 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157892</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155199</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154173</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151119</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151131</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157892</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154688</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>312065</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>308725</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>313405</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>312065</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>309332</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>313405</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3811,47 +3811,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4903</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4745</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746791</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>743418</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705131</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>702025</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>706491</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701744</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>706486</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>746791</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>743397</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2079</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1447737</t>
+          <t>1447882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453967</t>
+          <t>1453949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4478</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3852</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3784</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130573</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>127748</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>127176</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>396</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252034</t>
+          <t>251966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6345</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3839</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6374</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3270</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3270</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7729</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5072,107 +5072,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>255550</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>251716</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>257332</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>209758</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>205981</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>206678</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>255550</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>251687</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>257386</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>465308</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>461457</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>467355</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>465308</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>460849</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>467282</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5307,102 +5307,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>479</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2393</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3215</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3973</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187928</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>185285</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188420</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>186504</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>186506</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>98,73%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187928</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>185357</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>533</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373498</t>
+          <t>373780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>717</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4278</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3926</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173331</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>170480</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>173331</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>169770</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>480</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343422</t>
+          <t>343221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8470</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2319</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5496</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8190</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>740972</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>736374</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>743485</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>702052</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698706</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>703887</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698875</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>703766</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>740972</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>736654</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>743461</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1437660</t>
+          <t>1438318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1446014</t>
+          <t>1446161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
